--- a/obspy/io/sitexml/tests/data/sera_site_no_owner.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_owner.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB6AC69-CF0B-7C48-B6A3-D4D820A7CF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7D0070-4462-D54A-8A7A-9CD2206127C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="siteDescription" sheetId="2" r:id="rId1"/>
@@ -74,9 +74,6 @@
     <t>siteClassEC8_description</t>
   </si>
   <si>
-    <t>siteClassEC8_url</t>
-  </si>
-  <si>
     <t>bedrockDepth_value</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>bedrockDepth_description</t>
   </si>
   <si>
-    <t>bedrockDepth_url</t>
-  </si>
-  <si>
     <t>h800_value</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>h800_description</t>
   </si>
   <si>
-    <t>h800_url</t>
-  </si>
-  <si>
     <t>geologicalUnit_value</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
   </si>
   <si>
     <t>geologicalUnit_description</t>
-  </si>
-  <si>
-    <t>geologicalUnit_url</t>
   </si>
   <si>
     <t>siteMorphology</t>
@@ -317,9 +305,6 @@
     <t>resonanceFrequency_description</t>
   </si>
   <si>
-    <t>resonanceFrequency_url</t>
-  </si>
-  <si>
     <t>velocityS30_value</t>
   </si>
   <si>
@@ -365,9 +350,6 @@
     <t>velocityS30_description</t>
   </si>
   <si>
-    <t>velocityS30_url</t>
-  </si>
-  <si>
     <t>velocityProfileCount</t>
   </si>
   <si>
@@ -407,9 +389,6 @@
     <t>velocityProfile_description</t>
   </si>
   <si>
-    <t>velocityProfile_url</t>
-  </si>
-  <si>
     <t>0.7</t>
   </si>
   <si>
@@ -510,6 +489,27 @@
   </si>
   <si>
     <t>quakeml:domain.ab/velocity_profile/006</t>
+  </si>
+  <si>
+    <t>siteClassEC8_uri</t>
+  </si>
+  <si>
+    <t>bedrockDepth_uri</t>
+  </si>
+  <si>
+    <t>h800_uri</t>
+  </si>
+  <si>
+    <t>geologicalUnit_uri</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_uri</t>
+  </si>
+  <si>
+    <t>velocityS30_uri</t>
+  </si>
+  <si>
+    <t>velocityProfile_uri</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1885,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>9</v>
@@ -1912,153 +1912,153 @@
         <v>16</v>
       </c>
       <c r="S1" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="T1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="V1" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="W1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="W1" s="9" t="s">
+      <c r="X1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="Y1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Z1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="AA1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AB1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AC1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AD1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="AF1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AG1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AH1" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AK1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AL1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AM1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AN1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AP1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AO1" s="9" t="s">
+      <c r="AQ1" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AR1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="AP1" s="9" t="s">
+      <c r="AS1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="AT1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AQ1" s="9" t="s">
+      <c r="AU1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AR1" s="9" t="s">
+      <c r="AV1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AS1" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="AT1" s="9" t="s">
+      <c r="AW1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="AU1" s="9" t="s">
+      <c r="AX1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="AV1" s="9" t="s">
+      <c r="AY1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AW1" s="9" t="s">
+      <c r="AZ1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AX1" s="9" t="s">
+      <c r="BA1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AY1" s="9" t="s">
+      <c r="BB1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AZ1" s="9" t="s">
+      <c r="BC1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="BA1" s="9" t="s">
+      <c r="BD1" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="BE1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="BB1" s="9" t="s">
+      <c r="BF1" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="BC1" s="9" t="s">
+      <c r="BG1" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="BD1" s="9" t="s">
+      <c r="BH1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="BE1" s="9" t="s">
+      <c r="BI1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="BF1" s="9" t="s">
+      <c r="BJ1" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="BG1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="BH1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="BI1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="BJ1" s="9" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:62" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="11" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F2" s="12">
         <v>239</v>
@@ -2066,35 +2066,35 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J2" s="12">
         <v>1</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="M2" s="13"/>
       <c r="N2" s="11">
         <v>2018</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="P2" s="17" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="T2" s="12">
         <v>40</v>
@@ -2103,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
@@ -2121,11 +2121,11 @@
         <v>1</v>
       </c>
       <c r="AH2" s="17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AI2" s="13"/>
       <c r="AJ2" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AK2" s="13"/>
       <c r="AL2" s="11"/>
@@ -2135,72 +2135,72 @@
       <c r="AP2" s="13"/>
       <c r="AQ2" s="13"/>
       <c r="AR2" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AS2" s="11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AT2" s="13"/>
       <c r="AU2" s="13"/>
       <c r="AV2" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="AW2" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AX2" s="13"/>
       <c r="AY2" s="11">
         <v>2018</v>
       </c>
       <c r="AZ2" s="11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="BA2" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB2" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="BC2" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="BD2" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="BE2" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="BG2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="BH2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BI2" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ2" s="17" t="s">
         <v>140</v>
-      </c>
-      <c r="BB2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="BC2" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="BD2" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="BE2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="BF2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="BG2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="BH2" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="BI2" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="BJ2" s="17" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="44" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="14" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F3" s="15">
         <v>120</v>
@@ -2208,33 +2208,33 @@
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
       <c r="I3" s="20" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J3" s="15">
         <v>1</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="M3" s="15"/>
       <c r="N3" s="11">
         <v>2023</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="R3" s="15"/>
       <c r="S3" s="14" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="T3" s="16">
         <v>820</v>
@@ -2244,27 +2244,27 @@
         <v>0.8</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="X3" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="Y3" s="15"/>
       <c r="Z3" s="11">
         <v>2023</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AC3" s="20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AD3" s="15"/>
       <c r="AE3" s="14" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AF3" s="16">
         <v>180</v>
@@ -2272,41 +2272,41 @@
       <c r="AG3" s="15"/>
       <c r="AH3" s="15"/>
       <c r="AI3" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="AJ3" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AK3" s="15"/>
       <c r="AL3" s="11">
         <v>2023</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AO3" s="20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AP3" s="15"/>
       <c r="AQ3" s="14" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AR3" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AS3" s="15"/>
       <c r="AT3" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AU3" s="15"/>
       <c r="AV3" s="14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AW3" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AX3" s="15"/>
       <c r="AY3" s="11"/>
@@ -2320,10 +2320,10 @@
       <c r="BG3" s="15"/>
       <c r="BH3" s="15"/>
       <c r="BI3" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="BJ3" s="20" t="s">
         <v>152</v>
-      </c>
-      <c r="BJ3" s="20" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2357,163 +2357,163 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AO1" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AQ1" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AS1" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AT1" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="AU1" s="2" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:47" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5">
         <v>0.8</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -2534,41 +2534,41 @@
         <v>0.5</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="X2" s="4">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="Z2" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AA2" s="5"/>
       <c r="AB2" s="11">
         <v>2018</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AD2" s="18" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AH2" s="4">
         <v>33</v>
@@ -2586,53 +2586,53 @@
         <v>1</v>
       </c>
       <c r="AM2" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="AN2" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AO2" s="5"/>
       <c r="AP2" s="3">
         <v>2018</v>
       </c>
       <c r="AQ2" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AR2" s="18" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AS2" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AT2" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AU2" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:47" ht="128" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7">
         <v>1</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
@@ -2653,41 +2653,41 @@
         <v>0.7</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="X3" s="8">
         <v>1</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="Z3" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AA3" s="7"/>
       <c r="AB3" s="11">
         <v>2018</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AD3" s="19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AF3" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AG3" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AH3" s="8">
         <v>33</v>
@@ -2705,53 +2705,53 @@
         <v>1</v>
       </c>
       <c r="AM3" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="AN3" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AO3" s="7"/>
       <c r="AP3" s="6">
         <v>2018</v>
       </c>
       <c r="AQ3" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AR3" s="19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AS3" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AT3" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AU3" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:47" ht="128" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>151</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7">
         <v>0.5</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -2772,41 +2772,41 @@
         <v>0.8</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="X4" s="8">
         <v>1</v>
       </c>
       <c r="Y4" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="Z4" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AA4" s="7"/>
       <c r="AB4" s="11">
         <v>2018</v>
       </c>
       <c r="AC4" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AD4" s="19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AF4" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AG4" s="19" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AH4" s="8">
         <v>33</v>
@@ -2824,74 +2824,74 @@
         <v>1</v>
       </c>
       <c r="AM4" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="AN4" s="17" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="AO4" s="7"/>
       <c r="AP4" s="6">
         <v>2018</v>
       </c>
       <c r="AQ4" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AR4" s="19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AS4" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AT4" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AU4" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:47" ht="44" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7">
         <v>0.6</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="11">
         <v>2023</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="N5" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P5" s="15"/>
       <c r="Q5" s="14" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="R5" s="8">
         <v>497</v>
@@ -2901,35 +2901,35 @@
         <v>0.8</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="6" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="17" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AA5" s="15"/>
       <c r="AB5" s="11">
         <v>2023</v>
       </c>
       <c r="AC5" s="21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="AD5" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AE5" s="20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AF5" s="15"/>
       <c r="AG5" s="14" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AH5" s="7"/>
       <c r="AI5" s="7"/>

--- a/obspy/io/sitexml/tests/data/sera_site_no_owner.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_owner.xlsx
@@ -1771,7 +1771,11 @@
           <t>0.43</t>
         </is>
       </c>
-      <c r="AI2" s="13" t="n"/>
+      <c r="AI2" s="13" t="inlineStr">
+        <is>
+          <t>Some title</t>
+        </is>
+      </c>
       <c r="AJ2" s="18" t="inlineStr">
         <is>
           <t>Author A.</t>

--- a/obspy/io/sitexml/tests/data/sera_site_no_owner.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_owner.xlsx
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>ABCD</t>
+          <t>XX.ABCD</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>ZWXY</t>
+          <t>YY.ZWXY</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">

--- a/obspy/io/sitexml/tests/data/sera_site_no_owner.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_owner.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFE0687-1FC4-4147-A673-F40EC578BBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9D83CD-3FB5-E64F-B557-62CB176E0B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="siteDescription" sheetId="1" r:id="rId1"/>
@@ -131,36 +131,6 @@
     <t>boreholeLogsCount</t>
   </si>
   <si>
-    <t>velocityProfileQindex1</t>
-  </si>
-  <si>
-    <t>velocityProfile_title</t>
-  </si>
-  <si>
-    <t>velocityProfile_firstAuthor</t>
-  </si>
-  <si>
-    <t>velocityProfile_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>velocityProfile_year</t>
-  </si>
-  <si>
-    <t>velocityProfile_booktitle</t>
-  </si>
-  <si>
-    <t>velocityProfile_language</t>
-  </si>
-  <si>
-    <t>velocityProfile_doi</t>
-  </si>
-  <si>
-    <t>velocityProfile_description</t>
-  </si>
-  <si>
-    <t>velocityProfile_uri</t>
-  </si>
-  <si>
     <t>quakeml:domain.ab/site/001</t>
   </si>
   <si>
@@ -498,6 +468,36 @@
   </si>
   <si>
     <t>Valley - Basin</t>
+  </si>
+  <si>
+    <t>velocityProfileSetQindex1</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_title</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_firstAuthor</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_secondaryAuthors</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_year</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_booktitle</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_language</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_doi</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_description</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_uri</t>
   </si>
 </sst>
 </file>
@@ -1808,201 +1808,201 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="BA1" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="BB1" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="BC1" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="BD1" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="BE1" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="BF1" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="BG1" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="BH1" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="BI1" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="BJ1" s="6" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:62" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F2" s="3">
         <v>239</v>
@@ -2010,35 +2010,35 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="2">
         <v>2018</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S2" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="T2" s="3">
         <v>40</v>
@@ -2047,7 +2047,7 @@
         <v>6</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
@@ -2065,13 +2065,13 @@
         <v>1</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AK2" s="3"/>
       <c r="AL2" s="2"/>
@@ -2081,72 +2081,72 @@
       <c r="AP2" s="3"/>
       <c r="AQ2" s="3"/>
       <c r="AR2" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="AT2" s="3"/>
       <c r="AU2" s="3"/>
       <c r="AV2" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AW2" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AX2" s="3"/>
       <c r="AY2" s="2">
         <v>2018</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="BA2" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BD2" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="BE2" s="7" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="BJ2" s="7" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:62" ht="44" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F3" s="5">
         <v>120</v>
@@ -2154,33 +2154,33 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="8" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="2">
         <v>2023</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="R3" s="5"/>
       <c r="S3" s="4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="T3" s="5">
         <v>820</v>
@@ -2190,27 +2190,27 @@
         <v>0.8</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Y3" s="5"/>
       <c r="Z3" s="2">
         <v>2023</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="AD3" s="5"/>
       <c r="AE3" s="4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="AF3" s="5">
         <v>180</v>
@@ -2218,41 +2218,41 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
       <c r="AI3" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AJ3" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK3" s="5"/>
       <c r="AL3" s="2">
         <v>2023</v>
       </c>
       <c r="AM3" s="9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="AN3" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="AP3" s="5"/>
       <c r="AQ3" s="4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="AR3" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="AS3" s="5"/>
       <c r="AT3" s="4" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="AU3" s="5"/>
       <c r="AV3" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="AW3" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="AX3" s="5"/>
       <c r="AY3" s="2"/>
@@ -2266,10 +2266,10 @@
       <c r="BG3" s="5"/>
       <c r="BH3" s="5"/>
       <c r="BI3" s="4" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="BJ3" s="8" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2404,58 +2404,58 @@
         <v>35</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>37</v>
+        <v>150</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:46" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3">
         <v>0.8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2476,41 +2476,41 @@
         <v>0.5</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="X2" s="3">
         <v>1</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AA2" s="3"/>
       <c r="AB2" s="2">
         <v>2018</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="AH2" s="3">
         <v>0</v>
@@ -2525,53 +2525,53 @@
         <v>1</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AN2" s="3"/>
       <c r="AO2" s="2">
         <v>2018</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AQ2" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:46" ht="128" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5">
         <v>1</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -2592,41 +2592,41 @@
         <v>0.7</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="X3" s="5">
         <v>1</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AA3" s="5"/>
       <c r="AB3" s="2">
         <v>2018</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AD3" s="8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="AH3" s="5">
         <v>0</v>
@@ -2641,53 +2641,53 @@
         <v>1</v>
       </c>
       <c r="AL3" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AM3" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AN3" s="5"/>
       <c r="AO3" s="4">
         <v>2018</v>
       </c>
       <c r="AP3" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AQ3" s="8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AR3" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AS3" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AT3" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:46" ht="128" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5">
         <v>0.5</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -2708,41 +2708,41 @@
         <v>0.8</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="X4" s="5">
         <v>1</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AA4" s="5"/>
       <c r="AB4" s="2">
         <v>2018</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="AH4" s="5">
         <v>0</v>
@@ -2757,74 +2757,74 @@
         <v>1</v>
       </c>
       <c r="AL4" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AM4" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AN4" s="5"/>
       <c r="AO4" s="4">
         <v>2018</v>
       </c>
       <c r="AP4" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AQ4" s="8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AR4" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AS4" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AT4" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:46" ht="44" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5">
         <v>0.6</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="2">
         <v>2023</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="P5" s="5"/>
       <c r="Q5" s="4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="R5" s="5">
         <v>497</v>
@@ -2834,35 +2834,35 @@
         <v>0.8</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA5" s="5"/>
       <c r="AB5" s="2">
         <v>2023</v>
       </c>
       <c r="AC5" s="9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="AD5" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="AF5" s="5"/>
       <c r="AG5" s="4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
